--- a/docs/FCC-core-55-70/FCC-core-UX-design-v1.0-2026-07-01.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-UX-design-v1.0-2026-07-01.xlsx
@@ -1340,12 +1340,12 @@
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Sandbox banner</t>
+          <t>'Trying it out' banner</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Soft violet strip pinned above scenario controls: '🧪 Scenario — nothing changes until you tap Use this plan'. Never dismissible.</t>
+          <t>Soft violet strip pinned above scenario controls: 'Trying it out — nothing changes until you tap Use this plan' (ONE wording on every scenario surface: Social Security, multi-goal, Roth, forward what-if). Never dismissible.</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
